--- a/CMBS_ABS-EE_scraping_data_dict.xlsx
+++ b/CMBS_ABS-EE_scraping_data_dict.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adminliveunc-my.sharepoint.com/personal/kieranf_ad_unc_edu/Documents/Documents/1. Research/Project 3 - CMBS/3. Data/EDGAR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="488" documentId="8_{2ACCB6B8-647D-4898-9216-507FEB12DAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D94B5461-007A-49B6-BE98-0F4348E1A0D7}"/>
+  <xr:revisionPtr revIDLastSave="490" documentId="8_{2ACCB6B8-647D-4898-9216-507FEB12DAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07996D13-4A15-4179-8584-4282FB464B38}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF389ACA-5DDE-4E23-BFCE-96C4A152E827}"/>
   </bookViews>
   <sheets>
     <sheet name="loan" sheetId="1" r:id="rId1"/>
     <sheet name="property" sheetId="2" r:id="rId2"/>
-    <sheet name="portfolio" sheetId="7" r:id="rId3"/>
-    <sheet name="XML schema" sheetId="6" r:id="rId4"/>
+    <sheet name="XML schema" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="532">
   <si>
     <t>variable</t>
   </si>
@@ -67,16 +66,10 @@
     <t>string</t>
   </si>
   <si>
-    <t xml:space="preserve">Not part of standard ABS-EE schema. Created by combining the trust's CIK number with the loan's assetNumber field. For collateral entries, this field is inherited from the associated loan. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Not part of standard ABS-EE schema. Created by combining the trust's CIK number with the loan's assetNumber field. For property entries, this field is inherited from the associated loan. </t>
   </si>
   <si>
     <t>propertyID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not part of standard ABS-EE schema. For single-property loans, this field is created appending "-001" to the loanID. For multi-property loans, this field is created by combining the deal's CIK with the property's assetNumber (e.g., "3-002"). </t>
   </si>
   <si>
     <t>NV</t>
@@ -1204,9 +1197,6 @@
     <t>https://www.sec.gov/submit-filings/technical-specifications#abs</t>
   </si>
   <si>
-    <t>Not part of standard ABS-EE schema. Inherited from associated loan.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Not part of standard ABS-EE schema. For single-property loans, this field will be the assetNumber of the associated loan. For non-loan entries (which are usually property details for loans secured by multiple properties) this field will be the listed assetNumber. </t>
   </si>
   <si>
@@ -1691,6 +1681,9 @@
   </si>
   <si>
     <t>The code that describes the type of loan modification. Enumerated values and descriptions: 1: Maturity Date Extension, 2: Amortization Change, 3: Principal Write-off, 5: Temporary Rate Reduction, 6: Capitalization on Interest, 7: Capitalization on Taxes, 8: Combination, 10: Forbearance, 98: Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not part of standard ABS-EE schema. For single-property loans, this field is the same as the loanID. For multi-property loans, this field is created by combining the loanID with the property's assetNumber (e.g., "3-002"). </t>
   </si>
 </sst>
 </file>
@@ -2189,7 +2182,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2200,62 +2193,62 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C4" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2271,1080 +2264,1080 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C11" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C12" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C13" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C15" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C16" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C17" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C18" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C19" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C20" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C21" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C24" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C25" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C26" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C30" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B31" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C31" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C33" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C34" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B35" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C35" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C36" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C37" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B38" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C38" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C39" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B40" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C40" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B42" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C42" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C43" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C44" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B45" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B46" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C46" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B47" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C47" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B48" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C48" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B49" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C49" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C50" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B51" t="s">
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B52" t="s">
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B53" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C53" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B54" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C54" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B55" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C55" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C56" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B57" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C57" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B58" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C58" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B59" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C59" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B60" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C60" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B61" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C61" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B62" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C62" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B63" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C63" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B64" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C64" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B65" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C65" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B66" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C66" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B67" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C67" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B68" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C68" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B69" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C69" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B70" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C70" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B71" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C71" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B72" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C72" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B73" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C73" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B74" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C74" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B75" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C75" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B76" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C76" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B77" t="s">
         <v>5</v>
       </c>
       <c r="C77" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B78" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C78" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B79" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C79" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B80" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C80" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B81" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C81" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B82" t="s">
         <v>5</v>
       </c>
       <c r="C82" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B83" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C83" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B84" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C84" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B85" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C85" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B86" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C86" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s">
         <v>5</v>
       </c>
       <c r="C87" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C88" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B89" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C89" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B90" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C90" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B91" t="s">
         <v>5</v>
       </c>
       <c r="C91" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B92" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C92" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C93" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B94" t="s">
         <v>5</v>
       </c>
       <c r="C94" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B95" t="s">
         <v>5</v>
       </c>
       <c r="C95" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B96" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C96" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B97" t="s">
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B98" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C98" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B99" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C99" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B100" t="s">
         <v>5</v>
       </c>
       <c r="C100" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B101" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C101" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B102" t="s">
         <v>5</v>
       </c>
       <c r="C102" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B103" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C103" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B104" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C104" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B105" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C105" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B106" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C106" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -3370,7 +3363,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -3381,62 +3374,62 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C4" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3447,623 +3440,623 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C18" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C19" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C20" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C21" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C22" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B23" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C23" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B24" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C24" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B26" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C26" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B27" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C27" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C28" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C30" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C31" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C33" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s">
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s">
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B36" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C36" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C37" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B38" t="s">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C39" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B40" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C40" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B42" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C42" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B43" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C43" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B44" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C44" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B45" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C45" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C46" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C47" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B48" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B49" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C49" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C50" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B51" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C51" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B52" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C52" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B53" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C53" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B54" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C54" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B55" t="s">
         <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B56" t="s">
         <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B57" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C57" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B58" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C58" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B59" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C59" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B60" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C60" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B61" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C61" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B63" t="s">
         <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B64" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C64" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -4072,713 +4065,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441AD334-7690-4FB4-A6B0-0D31DBC16962}">
-  <dimension ref="A1:C63"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="46.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>375</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>373</v>
-      </c>
-      <c r="B4" t="s">
-        <v>364</v>
-      </c>
-      <c r="C4" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>366</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>367</v>
-      </c>
-      <c r="B6" t="s">
-        <v>364</v>
-      </c>
-      <c r="C6" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>368</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>158</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>163</v>
-      </c>
-      <c r="B17" t="s">
-        <v>363</v>
-      </c>
-      <c r="C17" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18" t="s">
-        <v>363</v>
-      </c>
-      <c r="C18" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>167</v>
-      </c>
-      <c r="B19" t="s">
-        <v>363</v>
-      </c>
-      <c r="C19" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>169</v>
-      </c>
-      <c r="B20" t="s">
-        <v>363</v>
-      </c>
-      <c r="C20" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>171</v>
-      </c>
-      <c r="B21" t="s">
-        <v>363</v>
-      </c>
-      <c r="C21" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>173</v>
-      </c>
-      <c r="B22" t="s">
-        <v>363</v>
-      </c>
-      <c r="C22" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>175</v>
-      </c>
-      <c r="B23" t="s">
-        <v>365</v>
-      </c>
-      <c r="C23" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>177</v>
-      </c>
-      <c r="B24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>180</v>
-      </c>
-      <c r="B25" t="s">
-        <v>364</v>
-      </c>
-      <c r="C25" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>182</v>
-      </c>
-      <c r="B26" t="s">
-        <v>365</v>
-      </c>
-      <c r="C26" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>184</v>
-      </c>
-      <c r="B27" t="s">
-        <v>364</v>
-      </c>
-      <c r="C27" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>186</v>
-      </c>
-      <c r="B28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>189</v>
-      </c>
-      <c r="B29" t="s">
-        <v>365</v>
-      </c>
-      <c r="C29" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>191</v>
-      </c>
-      <c r="B30" t="s">
-        <v>365</v>
-      </c>
-      <c r="C30" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>193</v>
-      </c>
-      <c r="B31" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>196</v>
-      </c>
-      <c r="B32" t="s">
-        <v>364</v>
-      </c>
-      <c r="C32" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>198</v>
-      </c>
-      <c r="B33" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>201</v>
-      </c>
-      <c r="B34" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>203</v>
-      </c>
-      <c r="B35" t="s">
-        <v>363</v>
-      </c>
-      <c r="C35" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>205</v>
-      </c>
-      <c r="B36" t="s">
-        <v>364</v>
-      </c>
-      <c r="C36" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>207</v>
-      </c>
-      <c r="B37" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>209</v>
-      </c>
-      <c r="B38" t="s">
-        <v>363</v>
-      </c>
-      <c r="C38" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>211</v>
-      </c>
-      <c r="B39" t="s">
-        <v>364</v>
-      </c>
-      <c r="C39" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>213</v>
-      </c>
-      <c r="B40" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>215</v>
-      </c>
-      <c r="B41" t="s">
-        <v>363</v>
-      </c>
-      <c r="C41" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>217</v>
-      </c>
-      <c r="B42" t="s">
-        <v>364</v>
-      </c>
-      <c r="C42" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>219</v>
-      </c>
-      <c r="B43" t="s">
-        <v>364</v>
-      </c>
-      <c r="C43" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>221</v>
-      </c>
-      <c r="B44" t="s">
-        <v>364</v>
-      </c>
-      <c r="C44" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>223</v>
-      </c>
-      <c r="B45" t="s">
-        <v>364</v>
-      </c>
-      <c r="C45" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>225</v>
-      </c>
-      <c r="B46" t="s">
-        <v>365</v>
-      </c>
-      <c r="C46" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>227</v>
-      </c>
-      <c r="B47" t="s">
-        <v>365</v>
-      </c>
-      <c r="C47" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>229</v>
-      </c>
-      <c r="B48" t="s">
-        <v>365</v>
-      </c>
-      <c r="C48" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>231</v>
-      </c>
-      <c r="B49" t="s">
-        <v>365</v>
-      </c>
-      <c r="C49" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>233</v>
-      </c>
-      <c r="B50" t="s">
-        <v>365</v>
-      </c>
-      <c r="C50" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>235</v>
-      </c>
-      <c r="B51" t="s">
-        <v>365</v>
-      </c>
-      <c r="C51" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>237</v>
-      </c>
-      <c r="B52" t="s">
-        <v>365</v>
-      </c>
-      <c r="C52" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>239</v>
-      </c>
-      <c r="B53" t="s">
-        <v>365</v>
-      </c>
-      <c r="C53" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>241</v>
-      </c>
-      <c r="B54" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>244</v>
-      </c>
-      <c r="B55" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>247</v>
-      </c>
-      <c r="B56" t="s">
-        <v>365</v>
-      </c>
-      <c r="C56" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>249</v>
-      </c>
-      <c r="B57" t="s">
-        <v>365</v>
-      </c>
-      <c r="C57" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>251</v>
-      </c>
-      <c r="B58" t="s">
-        <v>365</v>
-      </c>
-      <c r="C58" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>253</v>
-      </c>
-      <c r="B59" t="s">
-        <v>365</v>
-      </c>
-      <c r="C59" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>255</v>
-      </c>
-      <c r="B60" t="s">
-        <v>365</v>
-      </c>
-      <c r="C60" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>257</v>
-      </c>
-      <c r="B61" t="s">
-        <v>5</v>
-      </c>
-      <c r="C61" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>260</v>
-      </c>
-      <c r="B62" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>263</v>
-      </c>
-      <c r="B63" t="s">
-        <v>364</v>
-      </c>
-      <c r="C63" t="s">
-        <v>426</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C165749-2F07-42AC-81BD-A55B73A92293}">
   <dimension ref="A1:I158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4796,42 +4082,42 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4842,22 +4128,22 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -4868,22 +4154,22 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4894,25 +4180,25 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -4923,25 +4209,25 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4952,25 +4238,25 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -4981,22 +4267,22 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
         <v>35</v>
       </c>
-      <c r="D9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" t="s">
-        <v>37</v>
-      </c>
       <c r="I9" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -5007,22 +4293,22 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -5033,25 +4319,25 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>150</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -5062,22 +4348,22 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -5088,25 +4374,25 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E13">
         <v>208</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -5117,25 +4403,25 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E14">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -5146,22 +4432,22 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -5172,25 +4458,25 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E16">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -5201,25 +4487,25 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E17">
         <v>208</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -5230,25 +4516,25 @@
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E18">
         <v>208</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -5259,22 +4545,22 @@
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" t="s">
         <v>57</v>
       </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" t="s">
-        <v>59</v>
-      </c>
       <c r="I19" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -5285,22 +4571,22 @@
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" t="s">
         <v>60</v>
       </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" t="s">
-        <v>62</v>
-      </c>
       <c r="I20" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -5311,25 +4597,25 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -5340,22 +4626,22 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -5366,22 +4652,22 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" t="s">
         <v>67</v>
       </c>
-      <c r="D23" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" t="s">
-        <v>29</v>
-      </c>
-      <c r="G23" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" t="s">
-        <v>69</v>
-      </c>
       <c r="I23" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -5392,22 +4678,22 @@
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" t="s">
         <v>70</v>
       </c>
-      <c r="F24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" t="s">
-        <v>72</v>
-      </c>
       <c r="I24" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -5418,22 +4704,22 @@
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" t="s">
         <v>73</v>
       </c>
-      <c r="F25" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" t="s">
-        <v>75</v>
-      </c>
       <c r="I25" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -5444,22 +4730,22 @@
         <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" t="s">
         <v>76</v>
       </c>
-      <c r="F26" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26" t="s">
-        <v>30</v>
-      </c>
-      <c r="H26" t="s">
-        <v>78</v>
-      </c>
       <c r="I26" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -5470,25 +4756,25 @@
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E27">
         <v>208</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G27" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H27" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -5499,25 +4785,25 @@
         <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E28">
         <v>208</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -5528,22 +4814,22 @@
         <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" t="s">
         <v>83</v>
       </c>
-      <c r="F29" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" t="s">
-        <v>85</v>
-      </c>
       <c r="I29" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -5554,25 +4840,25 @@
         <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E30">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -5583,25 +4869,25 @@
         <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E31">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G31" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H31" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -5612,25 +4898,25 @@
         <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E32">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -5641,22 +4927,22 @@
         <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -5667,22 +4953,22 @@
         <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F34" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -5693,22 +4979,22 @@
         <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F35" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -5719,22 +5005,22 @@
         <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -5745,22 +5031,22 @@
         <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G37" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -5771,22 +5057,22 @@
         <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G38" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" t="s">
         <v>102</v>
       </c>
-      <c r="F38" t="s">
-        <v>103</v>
-      </c>
-      <c r="G38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H38" t="s">
-        <v>104</v>
-      </c>
       <c r="I38" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -5797,22 +5083,22 @@
         <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -5823,22 +5109,22 @@
         <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F40" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -5849,25 +5135,25 @@
         <v>36</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E41">
         <v>208</v>
       </c>
       <c r="F41" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -5878,25 +5164,25 @@
         <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E42">
         <v>208</v>
       </c>
       <c r="F42" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H42" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -5907,25 +5193,25 @@
         <v>38</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E43">
         <v>208</v>
       </c>
       <c r="F43" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G43" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H43" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -5936,25 +5222,25 @@
         <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E44">
         <v>208</v>
       </c>
       <c r="F44" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -5965,25 +5251,25 @@
         <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D45" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E45">
         <v>208</v>
       </c>
       <c r="F45" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H45" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -5994,25 +5280,25 @@
         <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D46" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E46">
         <v>208</v>
       </c>
       <c r="F46" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -6023,25 +5309,25 @@
         <v>42</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E47">
         <v>208</v>
       </c>
       <c r="F47" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G47" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -6052,22 +5338,22 @@
         <v>43</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
+        <v>121</v>
+      </c>
+      <c r="F48" t="s">
+        <v>122</v>
+      </c>
+      <c r="G48" t="s">
+        <v>28</v>
+      </c>
+      <c r="H48" t="s">
         <v>123</v>
       </c>
-      <c r="F48" t="s">
-        <v>124</v>
-      </c>
-      <c r="G48" t="s">
-        <v>30</v>
-      </c>
-      <c r="H48" t="s">
-        <v>125</v>
-      </c>
       <c r="I48" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -6078,22 +5364,22 @@
         <v>44</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
+        <v>124</v>
+      </c>
+      <c r="F49" t="s">
+        <v>125</v>
+      </c>
+      <c r="G49" t="s">
+        <v>28</v>
+      </c>
+      <c r="H49" t="s">
         <v>126</v>
       </c>
-      <c r="F49" t="s">
-        <v>127</v>
-      </c>
-      <c r="G49" t="s">
-        <v>30</v>
-      </c>
-      <c r="H49" t="s">
-        <v>128</v>
-      </c>
       <c r="I49" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -6104,25 +5390,25 @@
         <v>45</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E50">
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H50" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -6133,22 +5419,22 @@
         <v>46</v>
       </c>
       <c r="C51" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D51" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F51" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H51" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -6159,22 +5445,22 @@
         <v>47</v>
       </c>
       <c r="C52" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F52" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G52" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H52" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -6185,22 +5471,22 @@
         <v>48</v>
       </c>
       <c r="C53" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F53" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H53" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -6211,25 +5497,25 @@
         <v>49</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D54" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E54">
         <v>208</v>
       </c>
       <c r="F54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H54" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -6240,25 +5526,25 @@
         <v>50</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D55" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E55">
         <v>208</v>
       </c>
       <c r="F55" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G55" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H55" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
@@ -6269,25 +5555,25 @@
         <v>51</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E56">
         <v>208</v>
       </c>
       <c r="F56" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H56" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -6298,25 +5584,25 @@
         <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D57" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E57">
         <v>208</v>
       </c>
       <c r="F57" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H57" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -6327,25 +5613,25 @@
         <v>53</v>
       </c>
       <c r="C58" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D58" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E58">
         <v>208</v>
       </c>
       <c r="F58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H58" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -6356,22 +5642,22 @@
         <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F59" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H59" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -6382,25 +5668,25 @@
         <v>55</v>
       </c>
       <c r="C60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E60">
         <v>150</v>
       </c>
       <c r="F60" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H60" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -6411,25 +5697,25 @@
         <v>56</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E61">
         <v>200</v>
       </c>
       <c r="F61" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G61" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H61" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -6440,25 +5726,25 @@
         <v>57</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E62">
         <v>50</v>
       </c>
       <c r="F62" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G62" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H62" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -6469,25 +5755,25 @@
         <v>58</v>
       </c>
       <c r="C63" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E63">
         <v>2</v>
       </c>
       <c r="F63" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H63" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -6498,25 +5784,25 @@
         <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E64">
         <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H64" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -6527,25 +5813,25 @@
         <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E65">
         <v>50</v>
       </c>
       <c r="F65" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H65" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -6556,22 +5842,22 @@
         <v>61</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
+        <v>158</v>
+      </c>
+      <c r="F66" t="s">
+        <v>159</v>
+      </c>
+      <c r="G66" t="s">
+        <v>28</v>
+      </c>
+      <c r="H66" t="s">
         <v>160</v>
       </c>
-      <c r="F66" t="s">
-        <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>30</v>
-      </c>
-      <c r="H66" t="s">
-        <v>162</v>
-      </c>
       <c r="I66" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -6582,25 +5868,25 @@
         <v>62</v>
       </c>
       <c r="C67" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D67" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E67">
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G67" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H67" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -6611,25 +5897,25 @@
         <v>63</v>
       </c>
       <c r="C68" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D68" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E68">
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H68" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -6640,25 +5926,25 @@
         <v>64</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D69" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E69">
         <v>8</v>
       </c>
       <c r="F69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H69" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -6669,25 +5955,25 @@
         <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D70" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E70">
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G70" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H70" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -6698,25 +5984,25 @@
         <v>66</v>
       </c>
       <c r="C71" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D71" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E71">
         <v>8</v>
       </c>
       <c r="F71" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G71" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H71" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -6727,25 +6013,25 @@
         <v>67</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E72">
         <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H72" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -6756,25 +6042,25 @@
         <v>68</v>
       </c>
       <c r="C73" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D73" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E73">
         <v>208</v>
       </c>
       <c r="F73" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G73" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H73" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -6785,22 +6071,22 @@
         <v>69</v>
       </c>
       <c r="C74" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D74" t="s">
+        <v>175</v>
+      </c>
+      <c r="F74" t="s">
+        <v>176</v>
+      </c>
+      <c r="G74" t="s">
+        <v>28</v>
+      </c>
+      <c r="H74" t="s">
         <v>177</v>
       </c>
-      <c r="F74" t="s">
-        <v>178</v>
-      </c>
-      <c r="G74" t="s">
-        <v>30</v>
-      </c>
-      <c r="H74" t="s">
-        <v>179</v>
-      </c>
       <c r="I74" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -6811,22 +6097,22 @@
         <v>70</v>
       </c>
       <c r="C75" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D75" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F75" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G75" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H75" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -6837,25 +6123,25 @@
         <v>71</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D76" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E76">
         <v>208</v>
       </c>
       <c r="F76" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G76" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H76" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -6866,22 +6152,22 @@
         <v>72</v>
       </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D77" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G77" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H77" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -6892,22 +6178,22 @@
         <v>73</v>
       </c>
       <c r="C78" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D78" t="s">
+        <v>184</v>
+      </c>
+      <c r="F78" t="s">
+        <v>185</v>
+      </c>
+      <c r="G78" t="s">
+        <v>28</v>
+      </c>
+      <c r="H78" t="s">
         <v>186</v>
       </c>
-      <c r="F78" t="s">
-        <v>187</v>
-      </c>
-      <c r="G78" t="s">
-        <v>30</v>
-      </c>
-      <c r="H78" t="s">
-        <v>188</v>
-      </c>
       <c r="I78" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -6918,25 +6204,25 @@
         <v>74</v>
       </c>
       <c r="C79" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D79" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E79">
         <v>208</v>
       </c>
       <c r="F79" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G79" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H79" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -6947,25 +6233,25 @@
         <v>75</v>
       </c>
       <c r="C80" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D80" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E80">
         <v>208</v>
       </c>
       <c r="F80" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G80" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H80" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -6976,22 +6262,22 @@
         <v>76</v>
       </c>
       <c r="C81" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
+        <v>191</v>
+      </c>
+      <c r="F81" t="s">
+        <v>192</v>
+      </c>
+      <c r="G81" t="s">
+        <v>28</v>
+      </c>
+      <c r="H81" t="s">
         <v>193</v>
       </c>
-      <c r="F81" t="s">
-        <v>194</v>
-      </c>
-      <c r="G81" t="s">
-        <v>30</v>
-      </c>
-      <c r="H81" t="s">
-        <v>195</v>
-      </c>
       <c r="I81" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -7002,22 +6288,22 @@
         <v>77</v>
       </c>
       <c r="C82" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D82" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G82" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H82" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -7028,22 +6314,22 @@
         <v>78</v>
       </c>
       <c r="C83" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D83" t="s">
+        <v>196</v>
+      </c>
+      <c r="F83" t="s">
+        <v>197</v>
+      </c>
+      <c r="G83" t="s">
+        <v>28</v>
+      </c>
+      <c r="H83" t="s">
         <v>198</v>
       </c>
-      <c r="F83" t="s">
-        <v>199</v>
-      </c>
-      <c r="G83" t="s">
-        <v>30</v>
-      </c>
-      <c r="H83" t="s">
-        <v>200</v>
-      </c>
       <c r="I83" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -7054,25 +6340,25 @@
         <v>79</v>
       </c>
       <c r="C84" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E84">
         <v>150</v>
       </c>
       <c r="F84" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H84" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -7083,25 +6369,25 @@
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D85" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E85">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H85" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -7112,22 +6398,22 @@
         <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D86" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F86" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G86" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H86" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -7138,25 +6424,25 @@
         <v>82</v>
       </c>
       <c r="C87" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E87">
         <v>150</v>
       </c>
       <c r="F87" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G87" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H87" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -7167,25 +6453,25 @@
         <v>83</v>
       </c>
       <c r="C88" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D88" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E88">
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G88" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H88" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -7196,22 +6482,22 @@
         <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D89" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G89" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H89" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -7222,25 +6508,25 @@
         <v>85</v>
       </c>
       <c r="C90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E90">
         <v>150</v>
       </c>
       <c r="F90" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G90" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H90" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -7251,25 +6537,25 @@
         <v>86</v>
       </c>
       <c r="C91" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D91" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E91">
         <v>8</v>
       </c>
       <c r="F91" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G91" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H91" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -7280,22 +6566,22 @@
         <v>87</v>
       </c>
       <c r="C92" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D92" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F92" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G92" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H92" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -7306,22 +6592,22 @@
         <v>88</v>
       </c>
       <c r="C93" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D93" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F93" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G93" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H93" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -7332,22 +6618,22 @@
         <v>89</v>
       </c>
       <c r="C94" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D94" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F94" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G94" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H94" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -7358,22 +6644,22 @@
         <v>90</v>
       </c>
       <c r="C95" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D95" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F95" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G95" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H95" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -7384,25 +6670,25 @@
         <v>91</v>
       </c>
       <c r="C96" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D96" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E96">
         <v>208</v>
       </c>
       <c r="F96" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G96" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H96" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -7413,25 +6699,25 @@
         <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D97" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E97">
         <v>208</v>
       </c>
       <c r="F97" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G97" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H97" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -7442,25 +6728,25 @@
         <v>93</v>
       </c>
       <c r="C98" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D98" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E98">
         <v>208</v>
       </c>
       <c r="F98" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G98" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H98" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -7471,25 +6757,25 @@
         <v>94</v>
       </c>
       <c r="C99" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D99" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E99">
         <v>208</v>
       </c>
       <c r="F99" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G99" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H99" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -7500,25 +6786,25 @@
         <v>95</v>
       </c>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D100" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E100">
         <v>208</v>
       </c>
       <c r="F100" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G100" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H100" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -7529,25 +6815,25 @@
         <v>96</v>
       </c>
       <c r="C101" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D101" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E101">
         <v>208</v>
       </c>
       <c r="F101" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G101" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H101" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -7558,25 +6844,25 @@
         <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D102" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E102">
         <v>208</v>
       </c>
       <c r="F102" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G102" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H102" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -7587,25 +6873,25 @@
         <v>98</v>
       </c>
       <c r="C103" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D103" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E103">
         <v>208</v>
       </c>
       <c r="F103" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G103" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H103" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -7616,22 +6902,22 @@
         <v>99</v>
       </c>
       <c r="C104" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D104" t="s">
+        <v>239</v>
+      </c>
+      <c r="F104" t="s">
+        <v>240</v>
+      </c>
+      <c r="G104" t="s">
+        <v>28</v>
+      </c>
+      <c r="H104" t="s">
         <v>241</v>
       </c>
-      <c r="F104" t="s">
-        <v>242</v>
-      </c>
-      <c r="G104" t="s">
-        <v>30</v>
-      </c>
-      <c r="H104" t="s">
-        <v>243</v>
-      </c>
       <c r="I104" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -7642,22 +6928,22 @@
         <v>100</v>
       </c>
       <c r="C105" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D105" t="s">
+        <v>242</v>
+      </c>
+      <c r="F105" t="s">
+        <v>243</v>
+      </c>
+      <c r="G105" t="s">
+        <v>28</v>
+      </c>
+      <c r="H105" t="s">
         <v>244</v>
       </c>
-      <c r="F105" t="s">
-        <v>245</v>
-      </c>
-      <c r="G105" t="s">
-        <v>30</v>
-      </c>
-      <c r="H105" t="s">
-        <v>246</v>
-      </c>
       <c r="I105" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -7668,22 +6954,22 @@
         <v>101</v>
       </c>
       <c r="C106" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D106" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F106" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G106" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H106" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -7694,25 +6980,25 @@
         <v>102</v>
       </c>
       <c r="C107" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D107" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E107">
         <v>208</v>
       </c>
       <c r="F107" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G107" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H107" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
@@ -7723,25 +7009,25 @@
         <v>103</v>
       </c>
       <c r="C108" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D108" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E108">
         <v>208</v>
       </c>
       <c r="F108" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G108" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H108" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -7752,25 +7038,25 @@
         <v>104</v>
       </c>
       <c r="C109" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D109" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E109">
         <v>208</v>
       </c>
       <c r="F109" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G109" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H109" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -7781,25 +7067,25 @@
         <v>105</v>
       </c>
       <c r="C110" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D110" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E110">
         <v>208</v>
       </c>
       <c r="F110" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G110" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H110" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -7810,22 +7096,22 @@
         <v>106</v>
       </c>
       <c r="C111" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D111" t="s">
+        <v>255</v>
+      </c>
+      <c r="F111" t="s">
+        <v>256</v>
+      </c>
+      <c r="G111" t="s">
+        <v>28</v>
+      </c>
+      <c r="H111" t="s">
         <v>257</v>
       </c>
-      <c r="F111" t="s">
-        <v>258</v>
-      </c>
-      <c r="G111" t="s">
-        <v>30</v>
-      </c>
-      <c r="H111" t="s">
-        <v>259</v>
-      </c>
       <c r="I111" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -7836,22 +7122,22 @@
         <v>107</v>
       </c>
       <c r="C112" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D112" t="s">
+        <v>258</v>
+      </c>
+      <c r="F112" t="s">
+        <v>259</v>
+      </c>
+      <c r="G112" t="s">
+        <v>28</v>
+      </c>
+      <c r="H112" t="s">
         <v>260</v>
       </c>
-      <c r="F112" t="s">
-        <v>261</v>
-      </c>
-      <c r="G112" t="s">
-        <v>30</v>
-      </c>
-      <c r="H112" t="s">
-        <v>262</v>
-      </c>
       <c r="I112" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -7862,22 +7148,22 @@
         <v>108</v>
       </c>
       <c r="C113" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D113" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F113" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G113" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H113" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -7888,22 +7174,22 @@
         <v>109</v>
       </c>
       <c r="C114" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D114" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F114" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G114" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H114" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -7914,22 +7200,22 @@
         <v>110</v>
       </c>
       <c r="C115" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D115" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F115" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G115" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H115" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -7940,25 +7226,25 @@
         <v>111</v>
       </c>
       <c r="C116" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D116" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E116">
         <v>208</v>
       </c>
       <c r="F116" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G116" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H116" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -7969,25 +7255,25 @@
         <v>112</v>
       </c>
       <c r="C117" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D117" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E117">
         <v>208</v>
       </c>
       <c r="F117" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G117" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H117" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -7998,25 +7284,25 @@
         <v>113</v>
       </c>
       <c r="C118" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D118" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E118">
         <v>208</v>
       </c>
       <c r="F118" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G118" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H118" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -8027,25 +7313,25 @@
         <v>114</v>
       </c>
       <c r="C119" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D119" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E119">
         <v>208</v>
       </c>
       <c r="F119" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G119" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H119" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -8056,25 +7342,25 @@
         <v>115</v>
       </c>
       <c r="C120" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D120" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E120">
         <v>208</v>
       </c>
       <c r="F120" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G120" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H120" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -8085,25 +7371,25 @@
         <v>116</v>
       </c>
       <c r="C121" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D121" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E121">
         <v>208</v>
       </c>
       <c r="F121" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G121" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H121" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -8114,25 +7400,25 @@
         <v>117</v>
       </c>
       <c r="C122" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D122" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E122">
         <v>208</v>
       </c>
       <c r="F122" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G122" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H122" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -8143,25 +7429,25 @@
         <v>118</v>
       </c>
       <c r="C123" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D123" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E123">
         <v>208</v>
       </c>
       <c r="F123" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G123" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H123" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -8172,25 +7458,25 @@
         <v>119</v>
       </c>
       <c r="C124" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D124" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E124">
         <v>208</v>
       </c>
       <c r="F124" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G124" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H124" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -8201,25 +7487,25 @@
         <v>120</v>
       </c>
       <c r="C125" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D125" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E125">
         <v>208</v>
       </c>
       <c r="F125" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G125" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H125" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -8230,25 +7516,25 @@
         <v>121</v>
       </c>
       <c r="C126" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D126" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E126">
         <v>208</v>
       </c>
       <c r="F126" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G126" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H126" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -8259,22 +7545,22 @@
         <v>122</v>
       </c>
       <c r="C127" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D127" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F127" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G127" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H127" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -8285,22 +7571,22 @@
         <v>123</v>
       </c>
       <c r="C128" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D128" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F128" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G128" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H128" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -8311,22 +7597,22 @@
         <v>124</v>
       </c>
       <c r="C129" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D129" t="s">
+        <v>293</v>
+      </c>
+      <c r="F129" t="s">
+        <v>294</v>
+      </c>
+      <c r="G129" t="s">
+        <v>28</v>
+      </c>
+      <c r="H129" t="s">
         <v>295</v>
       </c>
-      <c r="F129" t="s">
-        <v>296</v>
-      </c>
-      <c r="G129" t="s">
-        <v>30</v>
-      </c>
-      <c r="H129" t="s">
-        <v>297</v>
-      </c>
       <c r="I129" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
@@ -8337,22 +7623,22 @@
         <v>125</v>
       </c>
       <c r="C130" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D130" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F130" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G130" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H130" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -8363,25 +7649,25 @@
         <v>126</v>
       </c>
       <c r="C131" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D131" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E131">
         <v>208</v>
       </c>
       <c r="F131" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G131" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H131" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -8392,25 +7678,25 @@
         <v>127</v>
       </c>
       <c r="C132" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D132" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E132">
         <v>208</v>
       </c>
       <c r="F132" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G132" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H132" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
@@ -8421,25 +7707,25 @@
         <v>128</v>
       </c>
       <c r="C133" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D133" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E133">
         <v>208</v>
       </c>
       <c r="F133" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G133" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H133" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
@@ -8450,22 +7736,22 @@
         <v>129</v>
       </c>
       <c r="C134" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D134" t="s">
+        <v>304</v>
+      </c>
+      <c r="F134" t="s">
+        <v>305</v>
+      </c>
+      <c r="G134" t="s">
+        <v>28</v>
+      </c>
+      <c r="H134" t="s">
         <v>306</v>
       </c>
-      <c r="F134" t="s">
-        <v>307</v>
-      </c>
-      <c r="G134" t="s">
-        <v>30</v>
-      </c>
-      <c r="H134" t="s">
-        <v>308</v>
-      </c>
       <c r="I134" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
@@ -8476,25 +7762,25 @@
         <v>130</v>
       </c>
       <c r="C135" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D135" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E135">
         <v>208</v>
       </c>
       <c r="F135" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G135" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H135" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
@@ -8505,25 +7791,25 @@
         <v>131</v>
       </c>
       <c r="C136" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D136" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E136">
         <v>208</v>
       </c>
       <c r="F136" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G136" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H136" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
@@ -8534,22 +7820,22 @@
         <v>132</v>
       </c>
       <c r="C137" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D137" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F137" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G137" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H137" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
@@ -8560,22 +7846,22 @@
         <v>133</v>
       </c>
       <c r="C138" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D138" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F138" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G138" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H138" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
@@ -8586,25 +7872,25 @@
         <v>134</v>
       </c>
       <c r="C139" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D139" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E139">
         <v>30</v>
       </c>
       <c r="F139" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G139" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H139" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -8615,22 +7901,22 @@
         <v>135</v>
       </c>
       <c r="C140" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D140" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F140" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G140" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H140" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -8641,22 +7927,22 @@
         <v>136</v>
       </c>
       <c r="C141" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D141" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F141" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G141" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H141" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
@@ -8667,22 +7953,22 @@
         <v>137</v>
       </c>
       <c r="C142" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D142" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F142" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G142" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H142" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
@@ -8693,22 +7979,22 @@
         <v>138</v>
       </c>
       <c r="C143" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D143" t="s">
+        <v>323</v>
+      </c>
+      <c r="F143" t="s">
+        <v>324</v>
+      </c>
+      <c r="G143" t="s">
+        <v>28</v>
+      </c>
+      <c r="H143" t="s">
         <v>325</v>
       </c>
-      <c r="F143" t="s">
-        <v>326</v>
-      </c>
-      <c r="G143" t="s">
-        <v>30</v>
-      </c>
-      <c r="H143" t="s">
-        <v>327</v>
-      </c>
       <c r="I143" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
@@ -8719,25 +8005,25 @@
         <v>139</v>
       </c>
       <c r="C144" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D144" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E144">
         <v>208</v>
       </c>
       <c r="F144" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G144" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H144" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -8748,22 +8034,22 @@
         <v>140</v>
       </c>
       <c r="C145" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D145" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F145" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G145" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H145" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
@@ -8774,25 +8060,25 @@
         <v>141</v>
       </c>
       <c r="C146" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D146" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E146">
         <v>150</v>
       </c>
       <c r="F146" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G146" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H146" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
@@ -8803,22 +8089,22 @@
         <v>142</v>
       </c>
       <c r="C147" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D147" t="s">
+        <v>332</v>
+      </c>
+      <c r="F147" t="s">
+        <v>333</v>
+      </c>
+      <c r="G147" t="s">
+        <v>12</v>
+      </c>
+      <c r="H147" t="s">
         <v>334</v>
       </c>
-      <c r="F147" t="s">
-        <v>335</v>
-      </c>
-      <c r="G147" t="s">
-        <v>14</v>
-      </c>
-      <c r="H147" t="s">
-        <v>336</v>
-      </c>
       <c r="I147" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -8829,25 +8115,25 @@
         <v>143</v>
       </c>
       <c r="C148" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D148" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E148">
         <v>208</v>
       </c>
       <c r="F148" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G148" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H148" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -8858,22 +8144,22 @@
         <v>144</v>
       </c>
       <c r="C149" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D149" t="s">
+        <v>337</v>
+      </c>
+      <c r="F149" t="s">
+        <v>338</v>
+      </c>
+      <c r="G149" t="s">
+        <v>28</v>
+      </c>
+      <c r="H149" t="s">
         <v>339</v>
       </c>
-      <c r="F149" t="s">
-        <v>340</v>
-      </c>
-      <c r="G149" t="s">
-        <v>30</v>
-      </c>
-      <c r="H149" t="s">
-        <v>341</v>
-      </c>
       <c r="I149" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -8884,22 +8170,22 @@
         <v>145</v>
       </c>
       <c r="C150" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D150" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F150" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G150" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H150" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -8910,25 +8196,25 @@
         <v>146</v>
       </c>
       <c r="C151" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D151" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E151">
         <v>208</v>
       </c>
       <c r="F151" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G151" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H151" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -8939,22 +8225,22 @@
         <v>147</v>
       </c>
       <c r="C152" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D152" t="s">
+        <v>344</v>
+      </c>
+      <c r="F152" t="s">
+        <v>345</v>
+      </c>
+      <c r="G152" t="s">
+        <v>12</v>
+      </c>
+      <c r="H152" t="s">
         <v>346</v>
       </c>
-      <c r="F152" t="s">
-        <v>347</v>
-      </c>
-      <c r="G152" t="s">
-        <v>14</v>
-      </c>
-      <c r="H152" t="s">
-        <v>348</v>
-      </c>
       <c r="I152" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -8965,22 +8251,22 @@
         <v>148</v>
       </c>
       <c r="C153" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D153" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F153" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G153" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H153" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -8991,22 +8277,22 @@
         <v>149</v>
       </c>
       <c r="C154" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D154" t="s">
+        <v>349</v>
+      </c>
+      <c r="F154" t="s">
+        <v>350</v>
+      </c>
+      <c r="G154" t="s">
+        <v>12</v>
+      </c>
+      <c r="H154" t="s">
         <v>351</v>
       </c>
-      <c r="F154" t="s">
-        <v>352</v>
-      </c>
-      <c r="G154" t="s">
-        <v>14</v>
-      </c>
-      <c r="H154" t="s">
-        <v>353</v>
-      </c>
       <c r="I154" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -9017,25 +8303,25 @@
         <v>150</v>
       </c>
       <c r="C155" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D155" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E155">
         <v>208</v>
       </c>
       <c r="F155" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G155" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H155" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
@@ -9046,25 +8332,25 @@
         <v>151</v>
       </c>
       <c r="C156" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D156" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E156">
         <v>208</v>
       </c>
       <c r="F156" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G156" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H156" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -9075,22 +8361,22 @@
         <v>152</v>
       </c>
       <c r="C157" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D157" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F157" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G157" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H157" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9101,25 +8387,25 @@
         <v>153</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E158" s="8">
         <v>208</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I158" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
